--- a/Templates/PEATREST_input_sensitivity_analysis.xlsx
+++ b/Templates/PEATREST_input_sensitivity_analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://forestresearch-my.sharepoint.com/personal/jacob_osullivan_forestresearch_gov_uk/Documents/Turbines and trees/PEATREST/Templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="160" documentId="109_{2692C0AF-F37D-4242-A816-1D703B957833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEA66075-4C4F-4F6E-ABB4-EE2D914670D2}"/>
+  <xr:revisionPtr revIDLastSave="162" documentId="109_{2692C0AF-F37D-4242-A816-1D703B957833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6C713CF-9D68-40F7-8F9A-137826394F21}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66,9 +66,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <customWorkbookViews>
+    <customWorkbookView name="Jagadeesh And Dali  - Personal View" guid="{DA59FCE9-3342-40E5-9DAB-341AFC9E9804}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1020" windowHeight="596" activeSheetId="6"/>
+    <customWorkbookView name="soi450 - Personal View" guid="{7ADC3CB4-E91A-4D68-AA62-B94BAF7A6D27}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1020" windowHeight="565" activeSheetId="5"/>
     <customWorkbookView name="soi663 - Personal View" guid="{55FEC4CD-8C58-46CE-8DB2-DCE86527AF45}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1020" windowHeight="596" activeSheetId="5"/>
-    <customWorkbookView name="soi450 - Personal View" guid="{7ADC3CB4-E91A-4D68-AA62-B94BAF7A6D27}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1020" windowHeight="565" activeSheetId="5"/>
-    <customWorkbookView name="Jagadeesh And Dali  - Personal View" guid="{DA59FCE9-3342-40E5-9DAB-341AFC9E9804}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1020" windowHeight="596" activeSheetId="6"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -5919,111 +5919,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>34925</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>330200</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="34" name="Rectangle 135">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000022000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="11325225" y="1416050"/>
-          <a:ext cx="4397375" cy="514350"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="CCFFCC"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="0" anchor="t" upright="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:cs typeface="Arial"/>
-            </a:rPr>
-            <a:t>Note: </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="0" u="sng" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:cs typeface="Arial"/>
-            </a:rPr>
-            <a:t>Emissions from felling and timber removal</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:cs typeface="Arial"/>
-            </a:rPr>
-            <a:t>. CARLY REF FOR NEW HARVESTING</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="800" b="0" i="0" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:cs typeface="Arial"/>
-            </a:rPr>
-            <a:t> EMISSIONS FACTOR</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-GB" sz="800" b="0" i="0" strike="noStrike">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="Arial"/>
-            <a:cs typeface="Arial"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>1095375</xdr:colOff>
       <xdr:row>3</xdr:row>
@@ -8076,7 +7971,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>66</xdr:row>
-          <xdr:rowOff>82550</xdr:rowOff>
+          <xdr:rowOff>88900</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -8134,7 +8029,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>66</xdr:row>
-          <xdr:rowOff>82550</xdr:rowOff>
+          <xdr:rowOff>88900</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -8192,7 +8087,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>101</xdr:row>
-          <xdr:rowOff>101600</xdr:rowOff>
+          <xdr:rowOff>107950</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -8250,7 +8145,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>101</xdr:row>
-          <xdr:rowOff>101600</xdr:rowOff>
+          <xdr:rowOff>107950</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -8308,7 +8203,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>101</xdr:row>
-          <xdr:rowOff>101600</xdr:rowOff>
+          <xdr:rowOff>107950</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -8366,7 +8261,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>101</xdr:row>
-          <xdr:rowOff>101600</xdr:rowOff>
+          <xdr:rowOff>107950</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -8424,7 +8319,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>136</xdr:row>
-          <xdr:rowOff>101600</xdr:rowOff>
+          <xdr:rowOff>107950</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -8482,7 +8377,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>136</xdr:row>
-          <xdr:rowOff>101600</xdr:rowOff>
+          <xdr:rowOff>107950</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -8540,7 +8435,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>136</xdr:row>
-          <xdr:rowOff>101600</xdr:rowOff>
+          <xdr:rowOff>107950</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -8598,7 +8493,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>136</xdr:row>
-          <xdr:rowOff>101600</xdr:rowOff>
+          <xdr:rowOff>107950</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -9120,7 +9015,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>67</xdr:row>
-          <xdr:rowOff>158750</xdr:rowOff>
+          <xdr:rowOff>165100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -9178,7 +9073,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>67</xdr:row>
-          <xdr:rowOff>158750</xdr:rowOff>
+          <xdr:rowOff>165100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -9468,7 +9363,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>103</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -9526,7 +9421,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>103</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -9700,7 +9595,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>138</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -9758,7 +9653,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>138</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10540,7 +10435,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>71</xdr:row>
-          <xdr:rowOff>158750</xdr:rowOff>
+          <xdr:rowOff>165100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10598,7 +10493,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>71</xdr:row>
-          <xdr:rowOff>158750</xdr:rowOff>
+          <xdr:rowOff>165100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -10656,7 +10551,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>71</xdr:row>
-          <xdr:rowOff>158750</xdr:rowOff>
+          <xdr:rowOff>165100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -11226,15 +11121,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1225550</xdr:colOff>
+      <xdr:colOff>1228725</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>87313</xdr:rowOff>
+      <xdr:rowOff>84138</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>215900</xdr:colOff>
+      <xdr:colOff>219075</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -11252,8 +11147,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="9950450" y="2335213"/>
-          <a:ext cx="1381125" cy="576262"/>
+          <a:off x="9953625" y="1055688"/>
+          <a:ext cx="1381125" cy="582612"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -11746,7 +11641,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>52</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -11804,7 +11699,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>52</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -11860,7 +11755,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>1092200</xdr:colOff>
+          <xdr:colOff>1098550</xdr:colOff>
           <xdr:row>53</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
@@ -11920,7 +11815,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>53</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -11978,7 +11873,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>53</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -12094,7 +11989,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>55</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -12152,7 +12047,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>55</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -12268,7 +12163,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>56</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -12326,7 +12221,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>56</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -12442,7 +12337,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>57</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -12500,7 +12395,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>57</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -12558,7 +12453,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>86</xdr:row>
-          <xdr:rowOff>158750</xdr:rowOff>
+          <xdr:rowOff>165100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -12616,7 +12511,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>87</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -12674,7 +12569,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>87</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -13428,7 +13323,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>121</xdr:row>
-          <xdr:rowOff>158750</xdr:rowOff>
+          <xdr:rowOff>165100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -13602,7 +13497,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>123</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -13660,7 +13555,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>123</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -13718,7 +13613,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>123</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -13776,7 +13671,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>124</xdr:row>
-          <xdr:rowOff>158750</xdr:rowOff>
+          <xdr:rowOff>165100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -13950,7 +13845,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>125</xdr:row>
-          <xdr:rowOff>158750</xdr:rowOff>
+          <xdr:rowOff>165100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -14008,7 +13903,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>125</xdr:row>
-          <xdr:rowOff>177800</xdr:rowOff>
+          <xdr:rowOff>184150</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -14066,7 +13961,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>125</xdr:row>
-          <xdr:rowOff>177800</xdr:rowOff>
+          <xdr:rowOff>184150</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -14124,7 +14019,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>126</xdr:row>
-          <xdr:rowOff>158750</xdr:rowOff>
+          <xdr:rowOff>165100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -14182,7 +14077,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>126</xdr:row>
-          <xdr:rowOff>177800</xdr:rowOff>
+          <xdr:rowOff>184150</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -14240,7 +14135,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>126</xdr:row>
-          <xdr:rowOff>177800</xdr:rowOff>
+          <xdr:rowOff>184150</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -14356,7 +14251,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>157</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -14414,7 +14309,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>157</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -14704,7 +14599,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>160</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -14762,7 +14657,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>160</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -14820,7 +14715,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>160</xdr:row>
-          <xdr:rowOff>158750</xdr:rowOff>
+          <xdr:rowOff>165100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -14878,7 +14773,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>161</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -14936,7 +14831,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>161</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -14994,7 +14889,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>161</xdr:row>
-          <xdr:rowOff>158750</xdr:rowOff>
+          <xdr:rowOff>165100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15052,7 +14947,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>162</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15110,7 +15005,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>162</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15168,7 +15063,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>192</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15226,7 +15121,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>192</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15284,7 +15179,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>192</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15342,7 +15237,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>193</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15400,7 +15295,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>193</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15458,7 +15353,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>193</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15516,7 +15411,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>195</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15574,7 +15469,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>195</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15632,7 +15527,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>195</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15690,7 +15585,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>196</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15748,7 +15643,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>196</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15806,7 +15701,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>196</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15864,7 +15759,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>197</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15922,7 +15817,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>197</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -15980,7 +15875,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>197</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -16199,7 +16094,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>53</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -16257,7 +16152,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>53</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -16313,7 +16208,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>1092200</xdr:colOff>
+          <xdr:colOff>1098550</xdr:colOff>
           <xdr:row>54</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
@@ -16373,7 +16268,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>54</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -16431,7 +16326,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>54</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -16837,7 +16732,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>123</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -16895,7 +16790,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>123</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -16953,7 +16848,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>123</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -17011,7 +16906,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>123</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -17069,7 +16964,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>123</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -17127,7 +17022,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>123</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -17185,7 +17080,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>124</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -17591,7 +17486,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>159</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -17649,7 +17544,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>159</xdr:row>
-          <xdr:rowOff>25400</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -17707,7 +17602,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>193</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -17765,7 +17660,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>193</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -17823,7 +17718,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>194</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -17881,7 +17776,7 @@
           <xdr:col>5</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>194</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -17939,7 +17834,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>1085850</xdr:colOff>
           <xdr:row>194</xdr:row>
-          <xdr:rowOff>6350</xdr:rowOff>
+          <xdr:rowOff>12700</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -18514,15 +18409,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>215900</xdr:colOff>
+      <xdr:colOff>219075</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>466725</xdr:rowOff>
+      <xdr:rowOff>463550</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>53975</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:rowOff>158750</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -18539,8 +18434,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="11331575" y="2066925"/>
-          <a:ext cx="4410075" cy="542925"/>
+          <a:off x="11334750" y="787400"/>
+          <a:ext cx="4406900" cy="542925"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
